--- a/Skills.xlsx
+++ b/Skills.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96d58a0df60135d6/Dashboard 0.2/Tasks/CoverLettermaker/AB-Coder96/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1347" documentId="11_F25DC773A252ABDACC10489F515D40A65BDE58F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79A3F16B-150C-465C-A204-42F3A811C4D6}"/>
+  <xr:revisionPtr revIDLastSave="1352" documentId="11_F25DC773A252ABDACC10489F515D40A65BDE58F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE3DA708-C486-4B7F-A949-063D976BC021}"/>
   <bookViews>
-    <workbookView xWindow="3960" yWindow="340" windowWidth="21640" windowHeight="11260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="510" yWindow="0" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="264">
   <si>
     <t>Affilation 1</t>
   </si>
@@ -827,6 +827,9 @@
   </si>
   <si>
     <t>Helioscope</t>
+  </si>
+  <si>
+    <t>Apache Spark</t>
   </si>
 </sst>
 </file>
@@ -1175,7 +1178,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1210,6 +1212,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1226,10 +1229,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1496,54 +1495,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E14600FD-47EF-4ED6-920E-F631DA05A544}">
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.7265625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.81640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.81640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.26953125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="5.81640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.54296875" style="1"/>
-    <col min="8" max="8" width="5.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="5.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" style="1"/>
+    <col min="8" max="8" width="5.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="12.54296875" style="1"/>
+    <col min="12" max="12" width="5.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="12.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:12" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="48" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="47" t="s">
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-    </row>
-    <row r="2" spans="1:12" ht="42" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+    </row>
+    <row r="2" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="40" t="s">
         <v>132</v>
       </c>
       <c r="E2" s="16" t="s">
@@ -1571,14 +1570,14 @@
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="46">
-        <v>5</v>
-      </c>
-      <c r="C3" s="43" t="s">
+      <c r="B3" s="45">
+        <v>5</v>
+      </c>
+      <c r="C3" s="42" t="s">
         <v>36</v>
       </c>
       <c r="D3" s="18">
@@ -1609,14 +1608,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B4" s="12">
         <v>5</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="41" t="s">
         <v>37</v>
       </c>
       <c r="D4" s="19">
@@ -1647,7 +1646,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>103</v>
       </c>
@@ -1685,7 +1684,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>109</v>
       </c>
@@ -1713,17 +1712,17 @@
       <c r="I6" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="J6" s="38">
-        <v>5</v>
-      </c>
-      <c r="K6" s="1" t="s">
+      <c r="J6" s="53">
+        <v>5</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="7">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>110</v>
       </c>
@@ -1751,17 +1750,17 @@
       <c r="I7" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J7" s="38">
-        <v>5</v>
-      </c>
-      <c r="K7" s="1" t="s">
+      <c r="J7" s="53">
+        <v>5</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>67</v>
       </c>
       <c r="L7" s="9">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>111</v>
       </c>
@@ -1789,17 +1788,17 @@
       <c r="I8" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="J8" s="38">
+      <c r="J8" s="53">
         <v>4</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" s="8" t="s">
         <v>68</v>
       </c>
       <c r="L8" s="9">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>112</v>
       </c>
@@ -1827,17 +1826,17 @@
       <c r="I9" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="J9" s="38">
+      <c r="J9" s="53">
         <v>4</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" s="8" t="s">
         <v>63</v>
       </c>
       <c r="L9" s="9">
         <v>4.5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>113</v>
       </c>
@@ -1865,17 +1864,17 @@
       <c r="I10" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="J10" s="38">
-        <v>5</v>
-      </c>
-      <c r="K10" s="1" t="s">
+      <c r="J10" s="53">
+        <v>5</v>
+      </c>
+      <c r="K10" s="8" t="s">
         <v>64</v>
       </c>
       <c r="L10" s="9">
         <v>4.5</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>114</v>
       </c>
@@ -1903,17 +1902,17 @@
       <c r="I11" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="J11" s="38">
-        <v>5</v>
-      </c>
-      <c r="K11" s="1" t="s">
+      <c r="J11" s="53">
+        <v>5</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>65</v>
       </c>
       <c r="L11" s="9">
         <v>4.5</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>124</v>
       </c>
@@ -1941,17 +1940,17 @@
       <c r="I12" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="J12" s="38">
-        <v>5</v>
-      </c>
-      <c r="K12" s="1" t="s">
+      <c r="J12" s="53">
+        <v>5</v>
+      </c>
+      <c r="K12" s="8" t="s">
         <v>66</v>
       </c>
       <c r="L12" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>125</v>
       </c>
@@ -1973,17 +1972,17 @@
       <c r="I13" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="J13" s="38">
+      <c r="J13" s="53">
         <v>4</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" s="8" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="9">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>104</v>
       </c>
@@ -2005,17 +2004,17 @@
       <c r="I14" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="J14" s="38">
-        <v>5</v>
-      </c>
-      <c r="K14" s="1" t="s">
+      <c r="J14" s="53">
+        <v>5</v>
+      </c>
+      <c r="K14" s="8" t="s">
         <v>57</v>
       </c>
       <c r="L14" s="9">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>115</v>
       </c>
@@ -2037,24 +2036,24 @@
       <c r="I15" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="J15" s="38">
-        <v>5</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="J15" s="53">
+        <v>5</v>
+      </c>
+      <c r="K15" s="8" t="s">
         <v>69</v>
       </c>
       <c r="L15" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>121</v>
       </c>
       <c r="B16" s="12">
         <v>5</v>
       </c>
-      <c r="C16" s="44" t="s">
+      <c r="C16" s="43" t="s">
         <v>261</v>
       </c>
       <c r="D16" s="21">
@@ -2069,17 +2068,17 @@
       <c r="I16" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="J16" s="38">
-        <v>5</v>
-      </c>
-      <c r="K16" s="1" t="s">
+      <c r="J16" s="53">
+        <v>5</v>
+      </c>
+      <c r="K16" s="8" t="s">
         <v>61</v>
       </c>
       <c r="L16" s="9">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>108</v>
       </c>
@@ -2095,17 +2094,17 @@
       <c r="I17" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="J17" s="38">
-        <v>5</v>
-      </c>
-      <c r="K17" s="1" t="s">
+      <c r="J17" s="53">
+        <v>5</v>
+      </c>
+      <c r="K17" s="8" t="s">
         <v>59</v>
       </c>
       <c r="L17" s="9">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>117</v>
       </c>
@@ -2121,15 +2120,15 @@
       <c r="I18" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="J18" s="39"/>
-      <c r="K18" s="1" t="s">
+      <c r="J18" s="43"/>
+      <c r="K18" s="8" t="s">
         <v>60</v>
       </c>
       <c r="L18" s="9">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>105</v>
       </c>
@@ -2142,14 +2141,14 @@
       <c r="F19" s="12">
         <v>5</v>
       </c>
-      <c r="K19" s="10" t="s">
+      <c r="K19" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="L19" s="11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L19" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>106</v>
       </c>
@@ -2162,8 +2161,14 @@
       <c r="F20" s="12">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K20" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="L20" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>118</v>
       </c>
@@ -2177,7 +2182,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>120</v>
       </c>
@@ -2191,7 +2196,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>107</v>
       </c>
@@ -2205,7 +2210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>116</v>
       </c>
@@ -2219,7 +2224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>119</v>
       </c>
@@ -2233,7 +2238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>123</v>
       </c>
@@ -2247,7 +2252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>256</v>
       </c>
@@ -2261,7 +2266,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>257</v>
       </c>
@@ -2275,7 +2280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>93</v>
       </c>
@@ -2289,7 +2294,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E30" s="8" t="s">
         <v>93</v>
       </c>
@@ -2297,7 +2302,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E31" s="8" t="s">
         <v>94</v>
       </c>
@@ -2305,7 +2310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E32" s="8" t="s">
         <v>95</v>
       </c>
@@ -2313,7 +2318,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E33" s="8" t="s">
         <v>96</v>
       </c>
@@ -2321,7 +2326,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E34" s="8" t="s">
         <v>92</v>
       </c>
@@ -2329,7 +2334,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="35" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E35" s="10" t="s">
         <v>122</v>
       </c>
@@ -2354,16 +2359,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E53"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="56.1796875" style="26" customWidth="1"/>
-    <col min="2" max="2" width="80.81640625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="33.453125" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7265625" style="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.26953125" style="24" customWidth="1"/>
+    <col min="1" max="1" width="56.140625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="80.85546875" style="26" customWidth="1"/>
+    <col min="3" max="3" width="33.42578125" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" style="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>254</v>
       </c>
@@ -2380,7 +2385,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
         <v>251</v>
       </c>
@@ -2395,7 +2400,7 @@
       </c>
       <c r="E2" s="23"/>
     </row>
-    <row r="3" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
         <v>161</v>
       </c>
@@ -2410,7 +2415,7 @@
       </c>
       <c r="E3" s="23"/>
     </row>
-    <row r="4" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="29" t="s">
         <v>165</v>
       </c>
@@ -2425,14 +2430,14 @@
       </c>
       <c r="E4" s="23"/>
     </row>
-    <row r="5" spans="1:5" ht="8.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="51" t="s">
+    <row r="5" spans="1:5" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="50" t="s">
         <v>168</v>
       </c>
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="50" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="50" t="s">
         <v>170</v>
       </c>
       <c r="D5" s="31" t="s">
@@ -2440,23 +2445,23 @@
       </c>
       <c r="E5" s="23"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="52"/>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="51"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
       <c r="D6" s="30" t="s">
         <v>172</v>
       </c>
       <c r="E6" s="23"/>
     </row>
-    <row r="7" spans="1:5" ht="65.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="51" t="s">
+    <row r="7" spans="1:5" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="50" t="s">
         <v>173</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="50" t="s">
         <v>35</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -2464,23 +2469,23 @@
       </c>
       <c r="E7" s="27"/>
     </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="52"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="51"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
       <c r="D8" s="30" t="s">
         <v>175</v>
       </c>
       <c r="E8" s="23"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="51" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="50" t="s">
         <v>176</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="50" t="s">
         <v>177</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="C9" s="50" t="s">
         <v>178</v>
       </c>
       <c r="D9" s="31" t="s">
@@ -2488,23 +2493,23 @@
       </c>
       <c r="E9" s="23"/>
     </row>
-    <row r="10" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="52"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
+    <row r="10" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="51"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
       <c r="D10" s="30" t="s">
         <v>180</v>
       </c>
       <c r="E10" s="23"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="51" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="50" t="s">
         <v>181</v>
       </c>
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="50" t="s">
         <v>182</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="50" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="31" t="s">
@@ -2512,16 +2517,16 @@
       </c>
       <c r="E11" s="23"/>
     </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="52"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
+    <row r="12" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="51"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
       <c r="D12" s="30" t="s">
         <v>183</v>
       </c>
       <c r="E12" s="23"/>
     </row>
-    <row r="13" spans="1:5" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="29" t="s">
         <v>184</v>
       </c>
@@ -2536,14 +2541,14 @@
       </c>
       <c r="E13" s="23"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="51" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="50" t="s">
         <v>187</v>
       </c>
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="50" t="s">
         <v>189</v>
       </c>
       <c r="D14" s="31" t="s">
@@ -2551,23 +2556,23 @@
       </c>
       <c r="E14" s="23"/>
     </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="52"/>
-      <c r="B15" s="52"/>
-      <c r="C15" s="52"/>
+    <row r="15" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="51"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
       <c r="D15" s="30" t="s">
         <v>190</v>
       </c>
       <c r="E15" s="23"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="51" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="50" t="s">
         <v>191</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="50" t="s">
         <v>192</v>
       </c>
-      <c r="C16" s="51" t="s">
+      <c r="C16" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="31" t="s">
@@ -2575,16 +2580,16 @@
       </c>
       <c r="E16" s="23"/>
     </row>
-    <row r="17" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="52"/>
-      <c r="B17" s="52"/>
-      <c r="C17" s="52"/>
+    <row r="17" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="51"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="51"/>
       <c r="D17" s="30" t="s">
         <v>193</v>
       </c>
       <c r="E17" s="23"/>
     </row>
-    <row r="18" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:5" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="29" t="s">
         <v>194</v>
       </c>
@@ -2599,7 +2604,7 @@
       </c>
       <c r="E18" s="23"/>
     </row>
-    <row r="19" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="29" t="s">
         <v>26</v>
       </c>
@@ -2614,7 +2619,7 @@
       </c>
       <c r="E19" s="23"/>
     </row>
-    <row r="20" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:5" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="29" t="s">
         <v>13</v>
       </c>
@@ -2629,14 +2634,14 @@
       </c>
       <c r="E20" s="28"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="51" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="50" t="s">
         <v>199</v>
       </c>
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="50" t="s">
         <v>200</v>
       </c>
-      <c r="C21" s="51" t="s">
+      <c r="C21" s="50" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="31" t="s">
@@ -2644,16 +2649,16 @@
       </c>
       <c r="E21" s="23"/>
     </row>
-    <row r="22" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="52"/>
-      <c r="B22" s="52"/>
-      <c r="C22" s="52"/>
+    <row r="22" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="51"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="51"/>
       <c r="D22" s="30" t="s">
         <v>202</v>
       </c>
       <c r="E22" s="23"/>
     </row>
-    <row r="23" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:5" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="29" t="s">
         <v>203</v>
       </c>
@@ -2668,7 +2673,7 @@
       </c>
       <c r="E23" s="23"/>
     </row>
-    <row r="24" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:5" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="29" t="s">
         <v>206</v>
       </c>
@@ -2683,7 +2688,7 @@
       </c>
       <c r="E24" s="23"/>
     </row>
-    <row r="25" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="29" t="s">
         <v>208</v>
       </c>
@@ -2698,14 +2703,14 @@
       </c>
       <c r="E25" s="23"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="51" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="50" t="s">
         <v>210</v>
       </c>
-      <c r="B26" s="51" t="s">
+      <c r="B26" s="50" t="s">
         <v>211</v>
       </c>
-      <c r="C26" s="51" t="s">
+      <c r="C26" s="50" t="s">
         <v>151</v>
       </c>
       <c r="D26" s="31" t="s">
@@ -2713,16 +2718,16 @@
       </c>
       <c r="E26" s="23"/>
     </row>
-    <row r="27" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="52"/>
-      <c r="B27" s="52"/>
-      <c r="C27" s="52"/>
+    <row r="27" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="51"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="51"/>
       <c r="D27" s="30" t="s">
         <v>212</v>
       </c>
       <c r="E27" s="23"/>
     </row>
-    <row r="28" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:5" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="29" t="s">
         <v>213</v>
       </c>
@@ -2737,7 +2742,7 @@
       </c>
       <c r="E28" s="23"/>
     </row>
-    <row r="29" spans="1:5" ht="33.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:5" ht="33.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="29" t="s">
         <v>216</v>
       </c>
@@ -2752,14 +2757,14 @@
       </c>
       <c r="E29" s="23"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="51" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="51" t="s">
+      <c r="B30" s="50" t="s">
         <v>218</v>
       </c>
-      <c r="C30" s="51" t="s">
+      <c r="C30" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D30" s="31" t="s">
@@ -2767,32 +2772,32 @@
       </c>
       <c r="E30" s="23"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="53"/>
-      <c r="B31" s="53"/>
-      <c r="C31" s="53"/>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="52"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
       <c r="D31" s="31" t="s">
         <v>219</v>
       </c>
       <c r="E31" s="23"/>
     </row>
-    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="52"/>
-      <c r="B32" s="52"/>
-      <c r="C32" s="52"/>
+    <row r="32" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="51"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="51"/>
       <c r="D32" s="30" t="s">
         <v>220</v>
       </c>
       <c r="E32" s="23"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="51" t="s">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="51" t="s">
+      <c r="B33" s="50" t="s">
         <v>221</v>
       </c>
-      <c r="C33" s="51" t="s">
+      <c r="C33" s="50" t="s">
         <v>148</v>
       </c>
       <c r="D33" s="31" t="s">
@@ -2800,23 +2805,23 @@
       </c>
       <c r="E33" s="23"/>
     </row>
-    <row r="34" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="52"/>
-      <c r="B34" s="52"/>
-      <c r="C34" s="52"/>
+    <row r="34" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="51"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="51"/>
       <c r="D34" s="30" t="s">
         <v>222</v>
       </c>
       <c r="E34" s="23"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="51" t="s">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="50" t="s">
         <v>223</v>
       </c>
-      <c r="B35" s="51" t="s">
+      <c r="B35" s="50" t="s">
         <v>224</v>
       </c>
-      <c r="C35" s="51" t="s">
+      <c r="C35" s="50" t="s">
         <v>150</v>
       </c>
       <c r="D35" s="31" t="s">
@@ -2824,23 +2829,23 @@
       </c>
       <c r="E35" s="23"/>
     </row>
-    <row r="36" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="52"/>
-      <c r="B36" s="52"/>
-      <c r="C36" s="52"/>
+    <row r="36" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="51"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
       <c r="D36" s="30" t="s">
         <v>225</v>
       </c>
       <c r="E36" s="23"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="51" t="s">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="51" t="s">
+      <c r="B37" s="50" t="s">
         <v>226</v>
       </c>
-      <c r="C37" s="51" t="s">
+      <c r="C37" s="50" t="s">
         <v>33</v>
       </c>
       <c r="D37" s="31" t="s">
@@ -2848,16 +2853,16 @@
       </c>
       <c r="E37" s="23"/>
     </row>
-    <row r="38" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="52"/>
-      <c r="B38" s="52"/>
-      <c r="C38" s="52"/>
+    <row r="38" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="51"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="51"/>
       <c r="D38" s="30" t="s">
         <v>110</v>
       </c>
       <c r="E38" s="23"/>
     </row>
-    <row r="39" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="29" t="s">
         <v>158</v>
       </c>
@@ -2872,14 +2877,14 @@
       </c>
       <c r="E39" s="23"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="51" t="s">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="50" t="s">
         <v>152</v>
       </c>
-      <c r="B40" s="51" t="s">
+      <c r="B40" s="50" t="s">
         <v>228</v>
       </c>
-      <c r="C40" s="51" t="s">
+      <c r="C40" s="50" t="s">
         <v>7</v>
       </c>
       <c r="D40" s="31" t="s">
@@ -2887,16 +2892,16 @@
       </c>
       <c r="E40" s="23"/>
     </row>
-    <row r="41" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="52"/>
-      <c r="B41" s="52"/>
-      <c r="C41" s="52"/>
+    <row r="41" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="51"/>
+      <c r="B41" s="51"/>
+      <c r="C41" s="51"/>
       <c r="D41" s="30" t="s">
         <v>212</v>
       </c>
       <c r="E41" s="23"/>
     </row>
-    <row r="42" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:5" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="29" t="s">
         <v>229</v>
       </c>
@@ -2911,7 +2916,7 @@
       </c>
       <c r="E42" s="23"/>
     </row>
-    <row r="43" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:5" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="29" t="s">
         <v>231</v>
       </c>
@@ -2926,7 +2931,7 @@
       </c>
       <c r="E43" s="23"/>
     </row>
-    <row r="44" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:5" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="29" t="s">
         <v>234</v>
       </c>
@@ -2941,7 +2946,7 @@
       </c>
       <c r="E44" s="23"/>
     </row>
-    <row r="45" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:5" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="29" t="s">
         <v>237</v>
       </c>
@@ -2956,7 +2961,7 @@
       </c>
       <c r="E45" s="23"/>
     </row>
-    <row r="46" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="29" t="s">
         <v>240</v>
       </c>
@@ -2971,7 +2976,7 @@
       </c>
       <c r="E46" s="23"/>
     </row>
-    <row r="47" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="29" t="s">
         <v>14</v>
       </c>
@@ -2986,7 +2991,7 @@
       </c>
       <c r="E47" s="23"/>
     </row>
-    <row r="48" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="29" t="s">
         <v>31</v>
       </c>
@@ -3001,7 +3006,7 @@
       </c>
       <c r="E48" s="23"/>
     </row>
-    <row r="49" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="29" t="s">
         <v>243</v>
       </c>
@@ -3016,7 +3021,7 @@
       </c>
       <c r="E49" s="23"/>
     </row>
-    <row r="50" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:5" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="29" t="s">
         <v>244</v>
       </c>
@@ -3031,7 +3036,7 @@
       </c>
       <c r="E50" s="23"/>
     </row>
-    <row r="51" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="29" t="s">
         <v>4</v>
       </c>
@@ -3045,24 +3050,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="51" t="s">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="50" t="s">
         <v>248</v>
       </c>
-      <c r="B52" s="51" t="s">
+      <c r="B52" s="50" t="s">
         <v>249</v>
       </c>
-      <c r="C52" s="51" t="s">
+      <c r="C52" s="50" t="s">
         <v>25</v>
       </c>
       <c r="D52" s="31" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="52"/>
-      <c r="B53" s="52"/>
-      <c r="C53" s="52"/>
+    <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="51"/>
+      <c r="B53" s="51"/>
+      <c r="C53" s="51"/>
       <c r="D53" s="30" t="s">
         <v>250</v>
       </c>
@@ -3072,48 +3077,48 @@
     <sortCondition ref="D1:D50"/>
   </sortState>
   <mergeCells count="42">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:C38"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
     <mergeCell ref="C40:C41"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="C52:C53"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
